--- a/Outputs/konstanterVolumenspeicher - 3 Wochen/Fehleranalyse_pypsa_trynsis.xlsx
+++ b/Outputs/konstanterVolumenspeicher - 3 Wochen/Fehleranalyse_pypsa_trynsis.xlsx
@@ -477,25 +477,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.596248149356473</v>
+        <v>1.59624815611719</v>
       </c>
       <c r="C2" t="n">
-        <v>2.542791457688672</v>
+        <v>2.542791460581618</v>
       </c>
       <c r="D2" t="n">
-        <v>4.24072982394996</v>
+        <v>4.240729828774658</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.6651215268954962</v>
+        <v>-0.6651215329823308</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.109253646077888</v>
+        <v>-1.109253656229181</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7093864719249279</v>
+        <v>0.7093864720644957</v>
       </c>
       <c r="H2" t="n">
-        <v>11.96956101759623</v>
+        <v>11.9695610208578</v>
       </c>
       <c r="I2" t="n">
         <v>301</v>
@@ -508,25 +508,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.756911913843477</v>
+        <v>1.756911907939753</v>
       </c>
       <c r="C3" t="n">
-        <v>2.578264952855347</v>
+        <v>2.578264950509206</v>
       </c>
       <c r="D3" t="n">
-        <v>4.552346223787278</v>
+        <v>4.552346219644784</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.6372532024547152</v>
+        <v>-0.6372531956109031</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.12517420158014</v>
+        <v>-1.125174189496276</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7810568508571512</v>
+        <v>0.781056850213754</v>
       </c>
       <c r="H3" t="n">
-        <v>11.77548175974825</v>
+        <v>11.77548177632841</v>
       </c>
       <c r="I3" t="n">
         <v>288</v>
@@ -539,25 +539,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.812814647305783</v>
+        <v>1.812814655772068</v>
       </c>
       <c r="C4" t="n">
-        <v>2.60777001451251</v>
+        <v>2.607770020456055</v>
       </c>
       <c r="D4" t="n">
-        <v>4.885288798231128</v>
+        <v>4.885288809365521</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.6582146502544521</v>
+        <v>-0.6582146594429028</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.233072180378148</v>
+        <v>-1.233072197591412</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7842108341900772</v>
+        <v>0.78421083415472</v>
       </c>
       <c r="H4" t="n">
-        <v>11.6980520767552</v>
+        <v>11.69805209899303</v>
       </c>
       <c r="I4" t="n">
         <v>289</v>
@@ -570,25 +570,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.718082006126268</v>
+        <v>1.718082009234028</v>
       </c>
       <c r="C5" t="n">
-        <v>2.543386716324811</v>
+        <v>2.543386718399693</v>
       </c>
       <c r="D5" t="n">
-        <v>4.488931720079016</v>
+        <v>4.488931723741064</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.6535298037835651</v>
+        <v>-0.653529806594056</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.153442631193805</v>
+        <v>-1.15344263615416</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7659022565728751</v>
+        <v>0.7659022563529836</v>
       </c>
       <c r="H5" t="n">
-        <v>11.72231245614473</v>
+        <v>11.72231247440246</v>
       </c>
       <c r="I5" t="n">
         <v>289</v>

--- a/Outputs/konstanterVolumenspeicher - 3 Wochen/Fehleranalyse_pypsa_trynsis.xlsx
+++ b/Outputs/konstanterVolumenspeicher - 3 Wochen/Fehleranalyse_pypsa_trynsis.xlsx
@@ -477,28 +477,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.59624815611719</v>
+        <v>0.8291310283636455</v>
       </c>
       <c r="C2" t="n">
-        <v>2.542791460581618</v>
+        <v>1.195143268082867</v>
       </c>
       <c r="D2" t="n">
-        <v>4.240729828774658</v>
+        <v>1.993395312702744</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.6651215329823308</v>
+        <v>-0.6591018365537591</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.109253656229181</v>
+        <v>-1.09932469743781</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7093864720644957</v>
+        <v>0.9625606980459848</v>
       </c>
       <c r="H2" t="n">
-        <v>11.9695610208578</v>
+        <v>3.6818897591466</v>
       </c>
       <c r="I2" t="n">
-        <v>301</v>
+        <v>297</v>
       </c>
     </row>
     <row r="3">
@@ -508,28 +508,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.756911907939753</v>
+        <v>0.8322463470179441</v>
       </c>
       <c r="C3" t="n">
-        <v>2.578264950509206</v>
+        <v>1.11375299692385</v>
       </c>
       <c r="D3" t="n">
-        <v>4.552346219644784</v>
+        <v>1.96661535274176</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.6372531956109031</v>
+        <v>-0.6342799079124904</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.125174189496276</v>
+        <v>-1.119983163485593</v>
       </c>
       <c r="G3" t="n">
-        <v>0.781056850213754</v>
+        <v>0.973033690802113</v>
       </c>
       <c r="H3" t="n">
-        <v>11.77548177632841</v>
+        <v>3.171795714170003</v>
       </c>
       <c r="I3" t="n">
-        <v>288</v>
+        <v>295</v>
       </c>
     </row>
     <row r="4">
@@ -539,28 +539,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.812814655772068</v>
+        <v>0.8569758118703512</v>
       </c>
       <c r="C4" t="n">
-        <v>2.607770020456055</v>
+        <v>1.146369786101441</v>
       </c>
       <c r="D4" t="n">
-        <v>4.885288809365521</v>
+        <v>2.147666457361822</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.6582146594429028</v>
+        <v>-0.6556153955540139</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.233072197591412</v>
+        <v>-1.228262652271928</v>
       </c>
       <c r="G4" t="n">
-        <v>0.78421083415472</v>
+        <v>0.9726404297910343</v>
       </c>
       <c r="H4" t="n">
-        <v>11.69805209899303</v>
+        <v>3.306575923339146</v>
       </c>
       <c r="I4" t="n">
-        <v>289</v>
+        <v>294</v>
       </c>
     </row>
     <row r="5">
@@ -570,28 +570,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.718082009234028</v>
+        <v>0.8335671688257181</v>
       </c>
       <c r="C5" t="n">
-        <v>2.543386718399693</v>
+        <v>1.143321903498475</v>
       </c>
       <c r="D5" t="n">
-        <v>4.488931723741064</v>
+        <v>2.018035231525805</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.653529806594056</v>
+        <v>-0.6496657054035798</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.15344263615416</v>
+        <v>-1.146700923166769</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7659022563529836</v>
+        <v>0.970283672599409</v>
       </c>
       <c r="H5" t="n">
-        <v>11.72231247440246</v>
+        <v>3.181403976578693</v>
       </c>
       <c r="I5" t="n">
-        <v>289</v>
+        <v>294</v>
       </c>
     </row>
   </sheetData>
